--- a/payment_forms/028_stripe_donation_form--payment_forms.xlsx
+++ b/payment_forms/028_stripe_donation_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Stripe payment status</t>
+          <t>Stripe Donation Form Page 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stripe payment method</t>
+          <t>Stripe Donation Form Page 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Stripe payment message</t>
+          <t>Stripe Donation Form Page 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Additional info</t>
+          <t>Stripe Donation Form Page 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Payment info</t>
+          <t>Stripe Donation Form Page 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1217,8 +1217,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_10,_'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 10, 'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_5,_'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 5, 'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_10,_'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 10, 'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'usd',_'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'USD', 'value': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'eur',_'value':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'EUR', 'value': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'card',_'value':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'card', 'value': 'card'}</t>
+          <t>card</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'bank',_'value':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'bank', 'value': 'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'pending', 'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'succeeded',_'value':_'succeeded'}</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'succeeded', 'value': 'succeeded'}</t>
+          <t>succeeded</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'failed', 'value': 'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'success',_'value':_'success'}</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'success', 'value': 'success'}</t>
+          <t>success</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'error',_'value':_'error'}</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'error', 'value': 'error'}</t>
+          <t>error</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'one-time',_'value':_'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'one-time', 'value': 'one-time'}</t>
+          <t>one-time</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'recurring',_'value':_'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'recurring', 'value': 'recurring'}</t>
+          <t>recurring</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'usd',_'value':_'usd'}</t>
+          <t>usd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'USD', 'value': 'USD'}</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'eur',_'value':_'eur'}</t>
+          <t>eur</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'EUR', 'value': 'EUR'}</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'pending', 'value': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'succeeded',_'value':_'succeeded'}</t>
+          <t>succeeded</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'succeeded', 'value': 'succeeded'}</t>
+          <t>succeeded</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'failed',_'value':_'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'failed', 'value': 'failed'}</t>
+          <t>failed</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'card',_'value':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'card', 'value': 'card'}</t>
+          <t>card</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'bank',_'value':_'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'bank', 'value': 'bank'}</t>
+          <t>bank</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'success',_'value':_'success'}</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'success', 'value': 'success'}</t>
+          <t>success</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'error',_'value':_'error'}</t>
+          <t>error</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'error', 'value': 'error'}</t>
+          <t>error</t>
         </is>
       </c>
     </row>
